--- a/給与改定明細/給与改定明細_テンプレート.xlsx
+++ b/給与改定明細/給与改定明細_テンプレート.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改定明細" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'改定明細'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'改定明細'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -104,157 +104,64 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00808080"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="00808080"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="00808080"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00808080"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00808080"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00808080"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00808080"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,15 +527,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -641,7 +548,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>（改定前後 比較）</t>
+          <t>（月額・昇格に伴う改定前後の比較）</t>
         </is>
       </c>
     </row>
@@ -652,14 +559,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="20" t="n"/>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>社員番号</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="20" t="n"/>
+      <c r="F4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -668,14 +575,18 @@
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="20" t="n"/>
+      <c r="C5" s="5" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>役職</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="20" t="n"/>
+          <t>役職（改定前→後）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　→</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -683,23 +594,15 @@
           <t>改定適用日</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026年11月1日</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="n"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>通知日</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026年10月25日</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="n"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -746,8 +649,12 @@
           <t>基本給</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="B10" s="8" t="n">
+        <v>253000</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>264000</v>
+      </c>
       <c r="D10" s="9">
         <f>IF(AND(B10="",C10=""),"",N(C10)-N(B10))</f>
         <v/>
@@ -756,16 +663,24 @@
         <f>IF(N(B10)=0,"",D10/B10)</f>
         <v/>
       </c>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>昇格に伴う改定</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>役職手当</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
+          <t>特別手当</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>30000</v>
+      </c>
       <c r="D11" s="9">
         <f>IF(AND(B11="",C11=""),"",N(C11)-N(B11))</f>
         <v/>
@@ -774,12 +689,12 @@
         <f>IF(N(B11)=0,"",D11/B11)</f>
         <v/>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>職務手当</t>
+          <t>勤務手当</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -792,12 +707,12 @@
         <f>IF(N(B12)=0,"",D12/B12)</f>
         <v/>
       </c>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>資格手当</t>
+          <t>夜勤手当</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -810,16 +725,20 @@
         <f>IF(N(B13)=0,"",D13/B13)</f>
         <v/>
       </c>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>住宅手当</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
+          <t>職務手当</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>15000</v>
+      </c>
       <c r="D14" s="9">
         <f>IF(AND(B14="",C14=""),"",N(C14)-N(B14))</f>
         <v/>
@@ -828,16 +747,20 @@
         <f>IF(N(B14)=0,"",D14/B14)</f>
         <v/>
       </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>家族手当</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
+          <t>時間外手当（実績払い）</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>21588</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="D15" s="9">
         <f>IF(AND(B15="",C15=""),"",N(C15)-N(B15))</f>
         <v/>
@@ -846,15 +769,21 @@
         <f>IF(N(B15)=0,"",D15/B15)</f>
         <v/>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>改定後は廃止</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>通勤手当（非課税分含む）</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
+          <t>みなし時間外手当</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="9">
         <f>IF(AND(B16="",C16=""),"",N(C16)-N(B16))</f>
@@ -864,16 +793,24 @@
         <f>IF(N(B16)=0,"",D16/B16)</f>
         <v/>
       </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　時間分（超過分は別途支給）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>その他手当</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
+          <t>通勤手当（非課税）</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>9240</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>9240</v>
+      </c>
       <c r="D17" s="9">
         <f>IF(AND(B17="",C17=""),"",N(C17)-N(B17))</f>
         <v/>
@@ -882,7 +819,7 @@
         <f>IF(N(B17)=0,"",D17/B17)</f>
         <v/>
       </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -911,177 +848,74 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>【年額換算】（単位：円）</t>
+          <t>【コメント】</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>改定前</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>改定後</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>増減額</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>増減率</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>昇格に伴い、時間外手当の実績払いを廃止し、みなし時間外手当（固定）に変更します。みなし時間外手当に含む時間数を超えた時間外労働は、別途支給します。</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>月額合計 × 12</t>
-        </is>
-      </c>
-      <c r="B22" s="16">
-        <f>B18*12</f>
-        <v/>
-      </c>
-      <c r="C22" s="16">
-        <f>C18*12</f>
-        <v/>
-      </c>
-      <c r="D22" s="9">
-        <f>C22-B22</f>
-        <v/>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22=0,"",D22/B22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="5" t="n"/>
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>賞与（想定年額）</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9">
-        <f>IF(AND(B23="",C23=""),"",N(C23)-N(B23))</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>IF(N(B23)=0,"",D23/B23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="4" t="n"/>
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>年収合計（想定）</t>
-        </is>
-      </c>
-      <c r="B24" s="12">
-        <f>B22+N(B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="12">
-        <f>C22+N(C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="13">
-        <f>C24-B24</f>
-        <v/>
-      </c>
-      <c r="E24" s="14">
-        <f>IF(B24=0,"",D24/B24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="15" t="n"/>
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>【コメント】</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="22" t="n"/>
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>※社会保険料・税金等の控除は含みません。改定前は9月、改定後は10月の月額を基準にしています。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="n"/>
-      <c r="F28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="n"/>
-      <c r="F29" s="24" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="27" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>※上記は想定額です。社会保険料・税金等の控除後の手取額は別途となります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>会社名</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="20" t="n"/>
-    </row>
-    <row r="35">
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>代表者</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="20" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="E34:F34"/>
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A27:F30"/>
+    <mergeCell ref="A21:F24"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/給与改定明細/給与改定明細_テンプレート.xlsx
+++ b/給与改定明細/給与改定明細_テンプレート.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改定明細" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'改定明細'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'改定明細'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,10 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -108,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,34 +119,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -527,15 +512,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -559,14 +542,12 @@
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>社員番号</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="D4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -575,18 +556,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>役職（改定前→後）</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　　　　→</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -595,56 +574,44 @@
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>通知日</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>【月額】（単位：円）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>改定前</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>改定後</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>増減額</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>増減率</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>基本給</t>
         </is>
@@ -655,22 +622,14 @@
       <c r="C10" s="8" t="n">
         <v>264000</v>
       </c>
-      <c r="D10" s="9">
-        <f>IF(AND(B10="",C10=""),"",N(C10)-N(B10))</f>
-        <v/>
-      </c>
-      <c r="E10" s="10">
-        <f>IF(N(B10)=0,"",D10/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>昇格に伴う改定</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>特別手当</t>
         </is>
@@ -681,54 +640,30 @@
       <c r="C11" s="8" t="n">
         <v>30000</v>
       </c>
-      <c r="D11" s="9">
-        <f>IF(AND(B11="",C11=""),"",N(C11)-N(B11))</f>
-        <v/>
-      </c>
-      <c r="E11" s="10">
-        <f>IF(N(B11)=0,"",D11/B11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>勤務手当</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9">
-        <f>IF(AND(B12="",C12=""),"",N(C12)-N(B12))</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>IF(N(B12)=0,"",D12/B12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>夜勤手当</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
-      <c r="D13" s="9">
-        <f>IF(AND(B13="",C13=""),"",N(C13)-N(B13))</f>
-        <v/>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(N(B13)=0,"",D13/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>職務手当</t>
         </is>
@@ -739,18 +674,10 @@
       <c r="C14" s="8" t="n">
         <v>15000</v>
       </c>
-      <c r="D14" s="9">
-        <f>IF(AND(B14="",C14=""),"",N(C14)-N(B14))</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>IF(N(B14)=0,"",D14/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>時間外手当（実績払い）</t>
         </is>
@@ -761,22 +688,14 @@
       <c r="C15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="9">
-        <f>IF(AND(B15="",C15=""),"",N(C15)-N(B15))</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>IF(N(B15)=0,"",D15/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>改定後は廃止</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>みなし時間外手当</t>
         </is>
@@ -785,22 +704,14 @@
         <v>0</v>
       </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="9">
-        <f>IF(AND(B16="",C16=""),"",N(C16)-N(B16))</f>
-        <v/>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(N(B16)=0,"",D16/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　時間分（超過分は別途支給）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>通勤手当（非課税）</t>
         </is>
@@ -811,112 +722,80 @@
       <c r="C17" s="8" t="n">
         <v>9240</v>
       </c>
-      <c r="D17" s="9">
-        <f>IF(AND(B17="",C17=""),"",N(C17)-N(B17))</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>IF(N(B17)=0,"",D17/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>月額合計</t>
         </is>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <f>SUM(B10:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="10">
         <f>SUM(C10:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="13">
-        <f>C18-B18</f>
-        <v/>
-      </c>
-      <c r="E18" s="14">
-        <f>IF(B18=0,"",D18/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="15" t="n"/>
+      <c r="D18" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>【コメント】</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>昇格に伴い、時間外手当の実績払いを廃止し、みなし時間外手当（固定）に変更します。みなし時間外手当に含む時間数を超えた時間外労働は、別途支給します。</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>※社会保険料・税金等の控除は含みません。改定前は9月、改定後は10月の月額を基準にしています。</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>※社会保険料・税金等の控除は含みません。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="D28" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>会社名</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="D28" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A21:F24"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B4:C4"/>
+  <mergeCells count="4">
+    <mergeCell ref="A21:D24"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
